--- a/market_scout_data.xlsx
+++ b/market_scout_data.xlsx
@@ -188,12 +188,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Summary'!$A$2</f>
+              <f>'Summary'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Summary'!$C$2</f>
+              <f>'Summary'!$C$2:$C$14</f>
             </numRef>
           </val>
         </ser>
@@ -212,12 +212,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Summary'!$A$2</f>
+              <f>'Summary'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Summary'!$D$2</f>
+              <f>'Summary'!$D$2:$D$14</f>
             </numRef>
           </val>
         </ser>
@@ -236,12 +236,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Summary'!$A$2</f>
+              <f>'Summary'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Summary'!$E$2</f>
+              <f>'Summary'!$E$2:$E$14</f>
             </numRef>
           </val>
         </ser>
@@ -260,12 +260,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Summary'!$A$2</f>
+              <f>'Summary'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Summary'!$F$2</f>
+              <f>'Summary'!$F$2:$F$14</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -944,6 +944,561 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 21:55</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Our top product updates from Sessions 2025 - Stripe</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 07 May 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://stripe.com/blog/top-product-updates-sessions-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 21:55</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Stripe publishes 2025 annual letter and announces tender offer to ...</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 24 Feb 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://stripe.com/newsroom/news/stripe-2025-update</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 21:55</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>[PDF] Stripe-annual-letter-2025-desktop.pdf</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 26 Feb 2026 10:39:32 GMT</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://assets.stripeassets.com/fzn2n1nzq965/3LlGw839Q6kUwxZlLZDtH6/75ddcbada4aa7743dd8ec7d0f9ca497e/Stripe-annual-letter-2025-desktop.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 21:55</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>All our product updates from Stripe Tour New York</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 30 Sep 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://stripe.com/blog/all-our-product-updates-from-stripe-tour-new-york</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 21:55</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Send your first Stripe API request</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 05 Jun 2024 16:25:45 GMT</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://docs.stripe.com/get-started/api-request</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 21:55</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>How to Integrate with Stripe API: A Step-by-Step Guide for Developers</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 09 Mar 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://unified.to/blog/how_to_integrate_with_stripe_api_a_step_by_step_guide_for_developers</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 21:55</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Tour of the API - Stripe Documentation</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 30 Mar 2024 03:24:42 GMT</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://docs.stripe.com/payments-api/tour</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 21:55</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Quickstart guides - Stripe Documentation</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 03 Oct 2025 05:26:40 GMT</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://docs.stripe.com/quickstarts</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Tesla Model 3: 2025 Vs. 2024 - What's New?</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 21:08:07 GMT</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://giftsandentertainment.roche.com/open-outlook/tesla-model-3-2025-vs-2024-whats-new-1767647287</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Tesla's latest software has some great new features</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 08 Apr 2025 16:30:05 GMT</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/electricvehicles/comments/1hafpa4/teslas_latest_software_has_some_great_new/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Tesla Unveils Exciting Features in 2025 Holiday Update ...</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 07 Dec 2025 06:31:55 GMT</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tesery.com/blogs/news/tesla-unveils-exciting-features-in-2025-holiday-update-but-some-expectations-are-unmet</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Tesla 2026.8 Software Update Spotted: What We Know So Far</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 12 Mar 2026 23:07:14 GMT</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.basenor.com/blogs/news/tesla-update-2026-8?srsltid=AfmBOoohs6TiN8uWWnBy2wS0ZWlPY8nWniZPo55TrsCs5CCQkc4a3Xmg</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Tesla launches official API documentation to support third-party apps</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 16 Oct 2023 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/tech/technology/tesla-launches-official-api-documentation-to-support-3rd-party-apps/articleshow/104464861.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Announcements | Tesla Fleet API</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 12 Dec 2025 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.tesla.com/docs/fleet-api/announcements</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Tesla releases official API documentation to support third-party apps</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 12 Oct 2023 12:42:46 GMT</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>https://electrek.co/2023/10/12/tesla-releases-official-api-documentation-support-third-party-apps/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -955,7 +1510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1011,6 +1566,294 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Track Stripe</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-04-08 14:21</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-04-08 14:31</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Nike latest features</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-04-08 14:34</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-04-08 17:42</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-04-08 20:22</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-04-08 20:40</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-04-08 20:56</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-04-08 21:10</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-04-08 21:20</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-04-08 21:23</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-04-08 21:55</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
         <v>0</v>
       </c>
     </row>

--- a/market_scout_data.xlsx
+++ b/market_scout_data.xlsx
@@ -188,12 +188,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Summary'!$A$2:$A$14</f>
+              <f>'Summary'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Summary'!$C$2:$C$14</f>
+              <f>'Summary'!$C$2:$C$18</f>
             </numRef>
           </val>
         </ser>
@@ -212,12 +212,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Summary'!$A$2:$A$14</f>
+              <f>'Summary'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Summary'!$D$2:$D$14</f>
+              <f>'Summary'!$D$2:$D$18</f>
             </numRef>
           </val>
         </ser>
@@ -236,12 +236,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Summary'!$A$2:$A$14</f>
+              <f>'Summary'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Summary'!$E$2:$E$14</f>
+              <f>'Summary'!$E$2:$E$18</f>
             </numRef>
           </val>
         </ser>
@@ -260,12 +260,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Summary'!$A$2:$A$14</f>
+              <f>'Summary'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Summary'!$F$2:$F$14</f>
+              <f>'Summary'!$F$2:$F$18</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1499,6 +1499,1227 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:57</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Here's Everything You Need to Know About Nike's 2024/2025 ...</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 21 Jun 2024 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sneakerfreaker.com/performance/releases/nike-2024-2025-snkrs-preview-everything-you-need-to-know-price-buy-release-date</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:57</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Nike 2024–2025 Releases Unveiled | SNKRDUNK Magazine</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 21 Jun 2024 03:52:07 GMT</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>https://snkrdunk.com/en/magazine/2024/06/21/nike-2024-2025-releases-unveiled/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:57</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Nike Releases Nike Blueprint Pack, Including Maxfly 2 ...</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 11 Apr 2024 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>https://about.nike.com/en/newsroom/releases/nike-air-blueprint-pack-official-images</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:57</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>NIKE, Inc. Newsroom: Press Releases, Product Announcements and ...</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 30 Nov 2023 19:16:44 GMT</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>https://about.nike.com/en/newsroom</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:57</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Nike Search Scraper API: Free Trial - Retailed</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.retailed.io/datasources/api/nike-search</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:57</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Nike To Open First-Ever API To Developers At Backplane's SXSW ...</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 11 Mar 2012 05:11:36 GMT</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2012/03/10/nike-apis-sxsw-backplane/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:57</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Path rolls out API, partners with Nike to appeal to runners - CNET</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 08 Mar 2012 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnet.com/tech/tech-industry/path-rolls-out-api-partners-with-nike-to-appeal-to-runners/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:57</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Nike API - Docs, SDKs &amp; Integration</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>https://apitracker.io/a/nike</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:59</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Here's Everything You Need to Know About Nike's 2024/2025 ...</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 21 Jun 2024 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sneakerfreaker.com/performance/releases/nike-2024-2025-snkrs-preview-everything-you-need-to-know-price-buy-release-date</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:59</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Nike 2024–2025 Releases Unveiled | SNKRDUNK Magazine</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 21 Jun 2024 03:52:07 GMT</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>https://snkrdunk.com/en/magazine/2024/06/21/nike-2024-2025-releases-unveiled/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:59</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Nike Releases Nike Blueprint Pack, Including Maxfly 2 ...</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 11 Apr 2024 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>https://about.nike.com/en/newsroom/releases/nike-air-blueprint-pack-official-images</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:59</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>NIKE, Inc. Newsroom: Press Releases, Product Announcements and ...</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 30 Nov 2023 19:16:44 GMT</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>https://about.nike.com/en/newsroom</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:59</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Nike Search Scraper API: Free Trial - Retailed</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.retailed.io/datasources/api/nike-search</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:59</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Nike To Open First-Ever API To Developers At Backplane's SXSW ...</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 11 Mar 2012 05:11:36 GMT</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2012/03/10/nike-apis-sxsw-backplane/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:59</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Path rolls out API, partners with Nike to appeal to runners - CNET</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 08 Mar 2012 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnet.com/tech/tech-industry/path-rolls-out-api-partners-with-nike-to-appeal-to-runners/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:59</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Nike API - Docs, SDKs &amp; Integration</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>https://apitracker.io/a/nike</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 23:12</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Here's Everything You Need to Know About Nike's 2024/2025 ...</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 21 Jun 2024 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sneakerfreaker.com/performance/releases/nike-2024-2025-snkrs-preview-everything-you-need-to-know-price-buy-release-date</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 23:12</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Nike 2024–2025 Releases Unveiled | SNKRDUNK Magazine</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 21 Jun 2024 03:52:07 GMT</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>https://snkrdunk.com/en/magazine/2024/06/21/nike-2024-2025-releases-unveiled/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 23:12</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Nike Releases Nike Blueprint Pack, Including Maxfly 2 ...</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 11 Apr 2024 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>https://about.nike.com/en/newsroom/releases/nike-air-blueprint-pack-official-images</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 23:12</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>NIKE, Inc. Newsroom: Press Releases, Product Announcements and ...</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 30 Nov 2023 19:16:44 GMT</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>https://about.nike.com/en/newsroom</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 23:12</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Nike Search Scraper API: Free Trial - Retailed</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.retailed.io/datasources/api/nike-search</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 23:12</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Nike To Open First-Ever API To Developers At Backplane's SXSW ...</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 11 Mar 2012 05:11:36 GMT</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2012/03/10/nike-apis-sxsw-backplane/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 23:12</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Path rolls out API, partners with Nike to appeal to runners - CNET</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 08 Mar 2012 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnet.com/tech/tech-industry/path-rolls-out-api-partners-with-nike-to-appeal-to-runners/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 23:12</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Nike API - Docs, SDKs &amp; Integration</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>https://apitracker.io/a/nike</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 23:15</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Tesla Update May 2024. Some very cool new features: update 2024.14.3</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 02 May 2024 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=osOexsXoWHo</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 23:15</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Tesla Model 3: 2025 Vs. 2024 - What's New?</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 21:08:07 GMT</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>https://giftsandentertainment.roche.com/open-outlook/tesla-model-3-2025-vs-2024-whats-new-1767647287</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 23:15</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Exciting New Tesla Updates and Features for 2025: What to Expect - PimpMyEV</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 03 Feb 2025 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>https://pimpmyev.com/blogs/speed-style-carbon-fiber/exciting-new-tesla-updates-and-features-for-2025-what-to-expect?srsltid=AfmBOop8nT6LPfKgExp88B_oThBlsI29sa8l2YAWsjGACqZF8c5Z5DIK</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 23:15</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Tesla's latest software has some great new features</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 09 Dec 2024 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/electricvehicles/comments/1hafpa4/teslas_latest_software_has_some_great_new/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 23:15</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Tesla ships out update that brings massive change to two big features</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 05 Mar 2026 16:34:14 GMT</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.teslarati.com/tesla-ships-out-update-everyone-that-california-caused/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 23:15</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Tesla: Current and upcoming models, prices, specs, and more</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Jun 2025 07:13:29 GMT</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>https://electrek.co/guides/tesla/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 23:15</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Tesla launches official API documentation to support third-party apps</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 16 Oct 2023 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/tech/technology/tesla-launches-official-api-documentation-to-support-3rd-party-apps/articleshow/104464861.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 23:15</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Tesla releases API for solar, Powerwall, EV charger</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 05 Jan 2024 18:55:26 GMT</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>https://pv-magazine-usa.com/2024/01/05/tesla-releases-api-for-solar-powerwall-ev-charger/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 23:15</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Tesla releases official API documentation to support third-party apps | Electrek</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 12 Oct 2023 12:42:46 GMT</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>https://electrek.co/2023/10/12/tesla-releases-official-api-documentation-support-third-party-apps/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1510,7 +2731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1854,6 +3075,102 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:57</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:59</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>8</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-04-08 23:12</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-08 23:15</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
         <v>0</v>
       </c>
     </row>
